--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-dispenser-instruction-extension.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-dispenser-instruction-extension.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Fr Instructions au dispensateur</t>
+    <t>Extension - Fr Instructions au dispensateur</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Instructions au dispensateur : par exemple pour indiquer que le traitement doit être étiqueté dans une langue étrangère, etc …</t>
+    <t>Extension pour représenter les instructions au dispensateur : par exemple pour indiquer que le traitement doit être étiqueté dans une langue étrangère, etc …</t>
   </si>
   <si>
     <t>Purpose</t>
